--- a/ProyectoAsistencia/ReporteEquipos.xlsx
+++ b/ProyectoAsistencia/ReporteEquipos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
   <si>
     <t>Laboratorio</t>
   </si>
@@ -29,58 +29,73 @@
     <t>Estado</t>
   </si>
   <si>
-    <t>LAB-104</t>
+    <t>LAB-101</t>
+  </si>
+  <si>
+    <t>Teclado</t>
+  </si>
+  <si>
+    <t>EQ001</t>
+  </si>
+  <si>
+    <t>SN1234567890</t>
+  </si>
+  <si>
+    <t>OPERATIVO</t>
+  </si>
+  <si>
+    <t>CPU</t>
+  </si>
+  <si>
+    <t>EQ002</t>
+  </si>
+  <si>
+    <t>SN9876543210</t>
+  </si>
+  <si>
+    <t>EQ013</t>
+  </si>
+  <si>
+    <t>SN1122334455</t>
+  </si>
+  <si>
+    <t>PizarraDigital</t>
+  </si>
+  <si>
+    <t>EQ014</t>
+  </si>
+  <si>
+    <t>SN2233445566</t>
+  </si>
+  <si>
+    <t>NO OPERATIVO</t>
+  </si>
+  <si>
+    <t>EQ025</t>
+  </si>
+  <si>
+    <t>SN3344556677</t>
   </si>
   <si>
     <t>Monitor</t>
   </si>
   <si>
-    <t>EQ007</t>
+    <t>EQ026</t>
+  </si>
+  <si>
+    <t>SN4455667788</t>
+  </si>
+  <si>
+    <t>EQ037</t>
   </si>
   <si>
     <t>SN5566778899</t>
   </si>
   <si>
-    <t>OPERATIVO</t>
-  </si>
-  <si>
-    <t>Teclado</t>
-  </si>
-  <si>
-    <t>EQ008</t>
+    <t>EQ038</t>
   </si>
   <si>
     <t>SN6677889900</t>
-  </si>
-  <si>
-    <t>NO OPERATIVO</t>
-  </si>
-  <si>
-    <t>PizarraDigital</t>
-  </si>
-  <si>
-    <t>EQ019</t>
-  </si>
-  <si>
-    <t>SN7788990011</t>
-  </si>
-  <si>
-    <t>EQ020</t>
-  </si>
-  <si>
-    <t>SN8899001122</t>
-  </si>
-  <si>
-    <t>EQ031</t>
-  </si>
-  <si>
-    <t>SN9900112233</t>
-  </si>
-  <si>
-    <t>EQ032</t>
-  </si>
-  <si>
-    <t>SN0011223344</t>
   </si>
 </sst>
 </file>
@@ -125,7 +140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.0" customWidth="true"/>
@@ -183,7 +198,7 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -191,13 +206,13 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
         <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -208,16 +223,16 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
         <v>17</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -225,7 +240,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -242,16 +257,50 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
         <v>10</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
         <v>21</v>
       </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>13</v>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
